--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/30.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/30.xlsx
@@ -426,13 +426,13 @@
         <v>-27.5240513326235</v>
       </c>
       <c r="E2">
-        <v>-12.60901717655483</v>
+        <v>-17.43213634553426</v>
       </c>
       <c r="F2">
-        <v>-2.614563755192545</v>
+        <v>-2.586402576966973</v>
       </c>
       <c r="G2">
-        <v>-8.996206710359889</v>
+        <v>-10.77878650870816</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-27.96071758761613</v>
       </c>
       <c r="E3">
-        <v>-13.23402810214548</v>
+        <v>-18.60473487660641</v>
       </c>
       <c r="F3">
-        <v>-2.597363534440817</v>
+        <v>-2.874396930061264</v>
       </c>
       <c r="G3">
-        <v>-8.934037975677915</v>
+        <v>-10.98508315398784</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-28.35794897282822</v>
       </c>
       <c r="E4">
-        <v>-14.00554874730628</v>
+        <v>-19.18256815998515</v>
       </c>
       <c r="F4">
-        <v>-2.535828261923855</v>
+        <v>-2.558412042426378</v>
       </c>
       <c r="G4">
-        <v>-8.774300842862541</v>
+        <v>-10.22085695842924</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-28.58231494542723</v>
       </c>
       <c r="E5">
-        <v>-14.01720051092802</v>
+        <v>-20.19727238783186</v>
       </c>
       <c r="F5">
-        <v>-2.537799776342518</v>
+        <v>-2.85336633843899</v>
       </c>
       <c r="G5">
-        <v>-8.562445791622421</v>
+        <v>-10.65123781017112</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-28.62502855414581</v>
       </c>
       <c r="E6">
-        <v>-15.28925791663064</v>
+        <v>-20.44308248544222</v>
       </c>
       <c r="F6">
-        <v>-2.437699859388226</v>
+        <v>-3.020610403594599</v>
       </c>
       <c r="G6">
-        <v>-8.327095798690094</v>
+        <v>-10.7375006952879</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-28.43124439375807</v>
       </c>
       <c r="E7">
-        <v>-16.39919595285866</v>
+        <v>-20.84798693189005</v>
       </c>
       <c r="F7">
-        <v>-2.601819322700475</v>
+        <v>-2.635346664961382</v>
       </c>
       <c r="G7">
-        <v>-8.321517529456422</v>
+        <v>-10.36966598041948</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-27.99864200471031</v>
       </c>
       <c r="E8">
-        <v>-16.30072881403587</v>
+        <v>-20.96447286878935</v>
       </c>
       <c r="F8">
-        <v>-2.697125477494767</v>
+        <v>-2.481584279286335</v>
       </c>
       <c r="G8">
-        <v>-8.349061268343158</v>
+        <v>-9.781987867924681</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-27.30546777467061</v>
       </c>
       <c r="E9">
-        <v>-17.31005774323548</v>
+        <v>-21.82721509436067</v>
       </c>
       <c r="F9">
-        <v>-2.345062704365754</v>
+        <v>-2.353180704913189</v>
       </c>
       <c r="G9">
-        <v>-7.837287343972764</v>
+        <v>-9.687226812408582</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-26.37916378538671</v>
       </c>
       <c r="E10">
-        <v>-17.76130659267781</v>
+        <v>-22.43500876177416</v>
       </c>
       <c r="F10">
-        <v>-2.555364478751479</v>
+        <v>-2.566382593576115</v>
       </c>
       <c r="G10">
-        <v>-7.502518357950583</v>
+        <v>-9.971940349876983</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-25.24004961165574</v>
       </c>
       <c r="E11">
-        <v>-18.58438391441594</v>
+        <v>-23.42901333493181</v>
       </c>
       <c r="F11">
-        <v>-2.16123803727571</v>
+        <v>-2.853225515980514</v>
       </c>
       <c r="G11">
-        <v>-7.085167813451283</v>
+        <v>-9.105739420072215</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-23.95549358697189</v>
       </c>
       <c r="E12">
-        <v>-19.46569741189272</v>
+        <v>-24.14708892985409</v>
       </c>
       <c r="F12">
-        <v>-2.19827268712007</v>
+        <v>-2.966184180128463</v>
       </c>
       <c r="G12">
-        <v>-7.118279889935073</v>
+        <v>-9.035734624098787</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-22.58781781817269</v>
       </c>
       <c r="E13">
-        <v>-19.50240069372489</v>
+        <v>-22.92597232826375</v>
       </c>
       <c r="F13">
-        <v>-2.14900553583857</v>
+        <v>-2.25864161833389</v>
       </c>
       <c r="G13">
-        <v>-6.490319059318417</v>
+        <v>-8.308520327669243</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-21.22891424144435</v>
       </c>
       <c r="E14">
-        <v>-20.01590700382467</v>
+        <v>-25.51198005271395</v>
       </c>
       <c r="F14">
-        <v>-1.73453273421524</v>
+        <v>-2.465377271050563</v>
       </c>
       <c r="G14">
-        <v>-6.163247091675042</v>
+        <v>-8.778313224056138</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.95640266031847</v>
       </c>
       <c r="E15">
-        <v>-21.5317412223082</v>
+        <v>-25.60032605212959</v>
       </c>
       <c r="F15">
-        <v>-1.796006707544394</v>
+        <v>-2.163655213357079</v>
       </c>
       <c r="G15">
-        <v>-5.698333939413033</v>
+        <v>-7.704633784214168</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.84393756094325</v>
       </c>
       <c r="E16">
-        <v>-22.01679513021778</v>
+        <v>-26.35663102462462</v>
       </c>
       <c r="F16">
-        <v>-1.527888201912875</v>
+        <v>-1.856615036937623</v>
       </c>
       <c r="G16">
-        <v>-5.966858909194396</v>
+        <v>-7.389178520868095</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.94541215779961</v>
       </c>
       <c r="E17">
-        <v>-23.14274132206292</v>
+        <v>-26.30204932741017</v>
       </c>
       <c r="F17">
-        <v>-1.04554063203896</v>
+        <v>-1.796021618157645</v>
       </c>
       <c r="G17">
-        <v>-5.968451281598786</v>
+        <v>-7.494923966483495</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.29057990009018</v>
       </c>
       <c r="E18">
-        <v>-23.60714086002352</v>
+        <v>-27.81386226097489</v>
       </c>
       <c r="F18">
-        <v>-1.081741115908701</v>
+        <v>-1.242181799585118</v>
       </c>
       <c r="G18">
-        <v>-4.880771544671238</v>
+        <v>-7.100684340393847</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.89376322155484</v>
       </c>
       <c r="E19">
-        <v>-24.56335078911316</v>
+        <v>-28.53022156424827</v>
       </c>
       <c r="F19">
-        <v>-0.4902528272463392</v>
+        <v>-1.462409072191186</v>
       </c>
       <c r="G19">
-        <v>-5.292464366843924</v>
+        <v>-7.130863273529842</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-16.73743412678598</v>
       </c>
       <c r="E20">
-        <v>-24.9189673244615</v>
+        <v>-28.42238954117762</v>
       </c>
       <c r="F20">
-        <v>-0.3516752444320099</v>
+        <v>-0.9120699342628894</v>
       </c>
       <c r="G20">
-        <v>-5.08979939002082</v>
+        <v>-6.790261106267466</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-16.79955002914138</v>
       </c>
       <c r="E21">
-        <v>-26.0423549284923</v>
+        <v>-29.67999658632176</v>
       </c>
       <c r="F21">
-        <v>-0.013327750391149</v>
+        <v>-0.7174947150193135</v>
       </c>
       <c r="G21">
-        <v>-5.223403076349188</v>
+        <v>-7.390218032167426</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.02791097074889</v>
       </c>
       <c r="E22">
-        <v>-26.03039975711205</v>
+        <v>-30.29235948400899</v>
       </c>
       <c r="F22">
-        <v>-0.03882241394710938</v>
+        <v>-0.2914753001683614</v>
       </c>
       <c r="G22">
-        <v>-4.863834793692327</v>
+        <v>-7.582809018914527</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.37909632045585</v>
       </c>
       <c r="E23">
-        <v>-26.57307396829524</v>
+        <v>-30.69695372998729</v>
       </c>
       <c r="F23">
-        <v>0.03285870251934023</v>
+        <v>-0.08070549820005518</v>
       </c>
       <c r="G23">
-        <v>-4.852145257393159</v>
+        <v>-7.568792169101253</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.78834868998983</v>
       </c>
       <c r="E24">
-        <v>-27.86694956176681</v>
+        <v>-31.40671731086849</v>
       </c>
       <c r="F24">
-        <v>0.3109068482082167</v>
+        <v>-0.288209047499123</v>
       </c>
       <c r="G24">
-        <v>-5.87168072494035</v>
+        <v>-7.815659549964705</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-18.20900739946268</v>
       </c>
       <c r="E25">
-        <v>-27.34542332419945</v>
+        <v>-30.90194642712951</v>
       </c>
       <c r="F25">
-        <v>0.2250813583389655</v>
+        <v>-0.02328804004241025</v>
       </c>
       <c r="G25">
-        <v>-5.615914597667337</v>
+        <v>-7.454863054912774</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-18.57891074794708</v>
       </c>
       <c r="E26">
-        <v>-27.79292259716343</v>
+        <v>-31.18625308227907</v>
       </c>
       <c r="F26">
-        <v>0.4664684478821443</v>
+        <v>0.3373259697857013</v>
       </c>
       <c r="G26">
-        <v>-5.527430336493697</v>
+        <v>-7.363564830030754</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.86053235770114</v>
       </c>
       <c r="E27">
-        <v>-28.21105924466167</v>
+        <v>-30.22479918028855</v>
       </c>
       <c r="F27">
-        <v>0.7998241999537353</v>
+        <v>0.07679199609421482</v>
       </c>
       <c r="G27">
-        <v>-5.541983494684333</v>
+        <v>-7.238138191184386</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-19.01357649545336</v>
       </c>
       <c r="E28">
-        <v>-27.22927249437671</v>
+        <v>-30.83557937631009</v>
       </c>
       <c r="F28">
-        <v>0.6014128112677949</v>
+        <v>0.02562871182770615</v>
       </c>
       <c r="G28">
-        <v>-5.45609801175902</v>
+        <v>-7.791320419159984</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-19.02565711970315</v>
       </c>
       <c r="E29">
-        <v>-28.01167506257795</v>
+        <v>-31.49451989340321</v>
       </c>
       <c r="F29">
-        <v>0.2903649933535946</v>
+        <v>0.3374063214237729</v>
       </c>
       <c r="G29">
-        <v>-5.423727497476026</v>
+        <v>-7.355861190560869</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-18.88695505925561</v>
       </c>
       <c r="E30">
-        <v>-27.39359723069304</v>
+        <v>-30.44851258897848</v>
       </c>
       <c r="F30">
-        <v>0.4887258516279642</v>
+        <v>-0.01420416310331087</v>
       </c>
       <c r="G30">
-        <v>-5.816272124249569</v>
+        <v>-7.883585323339472</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-18.61217042701557</v>
       </c>
       <c r="E31">
-        <v>-27.50160133577598</v>
+        <v>-30.97611377442713</v>
       </c>
       <c r="F31">
-        <v>0.2271274258238803</v>
+        <v>-0.04369735611258448</v>
       </c>
       <c r="G31">
-        <v>-5.52523544480116</v>
+        <v>-7.762104854775916</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-18.21905535844685</v>
       </c>
       <c r="E32">
-        <v>-27.14018382522381</v>
+        <v>-30.45352334546796</v>
       </c>
       <c r="F32">
-        <v>0.3757613889081956</v>
+        <v>0.07513526128861581</v>
       </c>
       <c r="G32">
-        <v>-5.787672321335805</v>
+        <v>-7.507017389338452</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-17.74015618181135</v>
       </c>
       <c r="E33">
-        <v>-27.08254993652819</v>
+        <v>-29.89017891467677</v>
       </c>
       <c r="F33">
-        <v>0.415658876496631</v>
+        <v>-0.221730906689657</v>
       </c>
       <c r="G33">
-        <v>-5.650827610924491</v>
+        <v>-7.675282487462989</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-17.207396848895</v>
       </c>
       <c r="E34">
-        <v>-26.28983150453748</v>
+        <v>-29.67182269073792</v>
       </c>
       <c r="F34">
-        <v>0.374086430019735</v>
+        <v>-0.2954837700305082</v>
       </c>
       <c r="G34">
-        <v>-5.116724056891713</v>
+        <v>-7.342420375671429</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.65519573391376</v>
       </c>
       <c r="E35">
-        <v>-25.79355150956288</v>
+        <v>-28.74728490885793</v>
       </c>
       <c r="F35">
-        <v>0.2819131607428312</v>
+        <v>-0.2394679095184</v>
       </c>
       <c r="G35">
-        <v>-5.402010318738408</v>
+        <v>-7.682512718920758</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.11627633743382</v>
       </c>
       <c r="E36">
-        <v>-25.04515325268524</v>
+        <v>-29.73557907629191</v>
       </c>
       <c r="F36">
-        <v>0.1403344028281593</v>
+        <v>-0.2835387120821393</v>
       </c>
       <c r="G36">
-        <v>-5.278275368662608</v>
+        <v>-7.614527355726285</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.61738033776479</v>
       </c>
       <c r="E37">
-        <v>-25.20738583401003</v>
+        <v>-29.42101315782309</v>
       </c>
       <c r="F37">
-        <v>0.2083085751670811</v>
+        <v>-0.2293957902677609</v>
       </c>
       <c r="G37">
-        <v>-4.843441833170416</v>
+        <v>-7.03248710228486</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.1861071982021</v>
       </c>
       <c r="E38">
-        <v>-24.60710943344927</v>
+        <v>-28.80576109371897</v>
       </c>
       <c r="F38">
-        <v>0.2435564365236029</v>
+        <v>-0.3289025961616486</v>
       </c>
       <c r="G38">
-        <v>-4.535362465285839</v>
+        <v>-7.074431714267426</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.83713880563264</v>
       </c>
       <c r="E39">
-        <v>-24.4973754512954</v>
+        <v>-28.42938150504546</v>
       </c>
       <c r="F39">
-        <v>0.234610896940771</v>
+        <v>-0.5368079036510742</v>
       </c>
       <c r="G39">
-        <v>-4.231669570240797</v>
+        <v>-7.221274272207339</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.58718408798621</v>
       </c>
       <c r="E40">
-        <v>-23.80968138849058</v>
+        <v>-27.48494107990176</v>
       </c>
       <c r="F40">
-        <v>0.2050663451525239</v>
+        <v>-0.4282188775528926</v>
       </c>
       <c r="G40">
-        <v>-4.904647199100461</v>
+        <v>-6.787341205101828</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.43354418058675</v>
       </c>
       <c r="E41">
-        <v>-23.56873034349046</v>
+        <v>-27.73606760599712</v>
       </c>
       <c r="F41">
-        <v>0.09238269898230431</v>
+        <v>-0.3358807631628317</v>
       </c>
       <c r="G41">
-        <v>-4.166779567125542</v>
+        <v>-5.817549994827727</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.37936504692408</v>
       </c>
       <c r="E42">
-        <v>-23.17763774276603</v>
+        <v>-27.12653047609069</v>
       </c>
       <c r="F42">
-        <v>0.1417525678217521</v>
+        <v>-0.7647116569788853</v>
       </c>
       <c r="G42">
-        <v>-3.917800058208035</v>
+        <v>-6.345568766159325</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.40757523649469</v>
       </c>
       <c r="E43">
-        <v>-22.65773722736742</v>
+        <v>-26.8595044777544</v>
       </c>
       <c r="F43">
-        <v>-0.2783191690770996</v>
+        <v>-0.7581642410271581</v>
       </c>
       <c r="G43">
-        <v>-4.3164162255006</v>
+        <v>-6.729247751978698</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.51005682961978</v>
       </c>
       <c r="E44">
-        <v>-23.03572442431365</v>
+        <v>-26.70739756431075</v>
       </c>
       <c r="F44">
-        <v>-0.1022041174049108</v>
+        <v>-0.5871262531667274</v>
       </c>
       <c r="G44">
-        <v>-4.534922162729116</v>
+        <v>-5.881638845922478</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.65866087276323</v>
       </c>
       <c r="E45">
-        <v>-22.36671937373849</v>
+        <v>-25.57609871618855</v>
       </c>
       <c r="F45">
-        <v>0.04207097640587354</v>
+        <v>-0.8380934117232823</v>
       </c>
       <c r="G45">
-        <v>-4.316025581126966</v>
+        <v>-7.220920043834637</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.83683847921084</v>
       </c>
       <c r="E46">
-        <v>-21.58780825899716</v>
+        <v>-25.98875591013751</v>
       </c>
       <c r="F46">
-        <v>-0.1199618294187238</v>
+        <v>-0.6891479824955145</v>
       </c>
       <c r="G46">
-        <v>-3.944694930169074</v>
+        <v>-6.513194928994782</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-15.0139640062625</v>
       </c>
       <c r="E47">
-        <v>-21.14293550095763</v>
+        <v>-24.4158402767873</v>
       </c>
       <c r="F47">
-        <v>-0.05479913604490345</v>
+        <v>-0.6706803596175023</v>
       </c>
       <c r="G47">
-        <v>-4.073591020740597</v>
+        <v>-6.496274730743567</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.17492380263072</v>
       </c>
       <c r="E48">
-        <v>-20.31951854366892</v>
+        <v>-24.21868410391536</v>
       </c>
       <c r="F48">
-        <v>-0.09550096838145715</v>
+        <v>-0.7543371836262244</v>
       </c>
       <c r="G48">
-        <v>-4.035043028481324</v>
+        <v>-6.595074651817575</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.29802991757429</v>
       </c>
       <c r="E49">
-        <v>-19.86847800403095</v>
+        <v>-23.42876426886139</v>
       </c>
       <c r="F49">
-        <v>-0.2260226782035613</v>
+        <v>-0.925557412315271</v>
       </c>
       <c r="G49">
-        <v>-4.377823534708541</v>
+        <v>-6.327350834056715</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.37721955057801</v>
       </c>
       <c r="E50">
-        <v>-19.69152788218123</v>
+        <v>-24.14646400044103</v>
       </c>
       <c r="F50">
-        <v>-0.5341960612300474</v>
+        <v>-0.5967659646331052</v>
       </c>
       <c r="G50">
-        <v>-4.340291879929824</v>
+        <v>-6.354606555481535</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.40524464528408</v>
       </c>
       <c r="E51">
-        <v>-19.82036296769945</v>
+        <v>-23.16981706815478</v>
       </c>
       <c r="F51">
-        <v>-0.08172024826848458</v>
+        <v>-0.7745510049893379</v>
       </c>
       <c r="G51">
-        <v>-4.425876103211063</v>
+        <v>-6.510331307103312</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.38645728246305</v>
       </c>
       <c r="E52">
-        <v>-18.88629727650733</v>
+        <v>-23.27902574732376</v>
       </c>
       <c r="F52">
-        <v>-0.1933734053896216</v>
+        <v>-1.024949903507572</v>
       </c>
       <c r="G52">
-        <v>-4.075431684060432</v>
+        <v>-7.394237034452101</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.32717298097279</v>
       </c>
       <c r="E53">
-        <v>-18.12312260894265</v>
+        <v>-22.23356412401695</v>
       </c>
       <c r="F53">
-        <v>-0.2505274427131762</v>
+        <v>-0.2804629839155448</v>
       </c>
       <c r="G53">
-        <v>-4.687475411724272</v>
+        <v>-7.103730042289976</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.23824813153985</v>
       </c>
       <c r="E54">
-        <v>-17.65279077003201</v>
+        <v>-22.46021877657486</v>
       </c>
       <c r="F54">
-        <v>-0.008871962131490458</v>
+        <v>-0.6677570510530229</v>
       </c>
       <c r="G54">
-        <v>-4.254131621724752</v>
+        <v>-6.698317325005287</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.13674075421252</v>
       </c>
       <c r="E55">
-        <v>-18.39638431598751</v>
+        <v>-21.23073808349235</v>
       </c>
       <c r="F55">
-        <v>-0.04980739407563363</v>
+        <v>-0.7018808178439456</v>
       </c>
       <c r="G55">
-        <v>-4.897056118178913</v>
+        <v>-7.248559788542011</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-15.03575301549854</v>
       </c>
       <c r="E56">
-        <v>-16.75599441992301</v>
+        <v>-23.01404661923893</v>
       </c>
       <c r="F56">
-        <v>0.07391507610429214</v>
+        <v>-0.4723451807326194</v>
       </c>
       <c r="G56">
-        <v>-5.0431968404645</v>
+        <v>-6.71538649780577</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.95480971723233</v>
       </c>
       <c r="E57">
-        <v>-17.03776060115426</v>
+        <v>-20.81082627418311</v>
       </c>
       <c r="F57">
-        <v>-0.07226360599812542</v>
+        <v>-1.045609386533392</v>
       </c>
       <c r="G57">
-        <v>-5.018811362022229</v>
+        <v>-6.927522945416728</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.90209586435088</v>
       </c>
       <c r="E58">
-        <v>-17.09939313239866</v>
+        <v>-21.01814887120227</v>
       </c>
       <c r="F58">
-        <v>-0.1146453674275565</v>
+        <v>-0.8580164761280132</v>
       </c>
       <c r="G58">
-        <v>-5.201013856867097</v>
+        <v>-7.791727616261314</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.89253282931011</v>
       </c>
       <c r="E59">
-        <v>-16.28263303190122</v>
+        <v>-21.3160726476929</v>
       </c>
       <c r="F59">
-        <v>-0.04255255236191555</v>
+        <v>-0.5006861146845989</v>
       </c>
       <c r="G59">
-        <v>-5.860994283939583</v>
+        <v>-7.313717945845947</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.92438589953901</v>
       </c>
       <c r="E60">
-        <v>-15.77634058089566</v>
+        <v>-20.48444103855427</v>
       </c>
       <c r="F60">
-        <v>-0.05994246924888558</v>
+        <v>-0.3203886359956754</v>
       </c>
       <c r="G60">
-        <v>-5.765518150587002</v>
+        <v>-7.35286183630229</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.00367123660645</v>
       </c>
       <c r="E61">
-        <v>-15.54837719934954</v>
+        <v>-20.54972351984885</v>
       </c>
       <c r="F61">
-        <v>-0.122183510793032</v>
+        <v>-0.5083070947903544</v>
       </c>
       <c r="G61">
-        <v>-5.815573599140782</v>
+        <v>-7.606615151887426</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.11860764087646</v>
       </c>
       <c r="E62">
-        <v>-15.41373208167947</v>
+        <v>-20.20019325356681</v>
       </c>
       <c r="F62">
-        <v>-0.2072601565301525</v>
+        <v>-0.2496460597965976</v>
       </c>
       <c r="G62">
-        <v>-6.019529688724202</v>
+        <v>-7.811607442224638</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-15.26752083667752</v>
       </c>
       <c r="E63">
-        <v>-15.04588413803641</v>
+        <v>-18.97643655163001</v>
       </c>
       <c r="F63">
-        <v>-0.09796536140478568</v>
+        <v>-0.6462228120498469</v>
       </c>
       <c r="G63">
-        <v>-5.960340445027572</v>
+        <v>-7.40051051824902</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.43121008386286</v>
       </c>
       <c r="E64">
-        <v>-14.71574479745522</v>
+        <v>-19.70284906720041</v>
       </c>
       <c r="F64">
-        <v>-0.2777873572045024</v>
+        <v>-0.6683924088509701</v>
       </c>
       <c r="G64">
-        <v>-6.176572037470609</v>
+        <v>-8.333597710129222</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.60199454998775</v>
       </c>
       <c r="E65">
-        <v>-14.21893044254771</v>
+        <v>-19.96525149357486</v>
       </c>
       <c r="F65">
-        <v>-0.07488207535837466</v>
+        <v>-0.6557366116709992</v>
       </c>
       <c r="G65">
-        <v>-6.585437653752757</v>
+        <v>-8.788125681034538</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.75709939196395</v>
       </c>
       <c r="E66">
-        <v>-14.79535084203606</v>
+        <v>-19.40543247979864</v>
       </c>
       <c r="F66">
-        <v>-0.05374710944334807</v>
+        <v>-0.9955668833628711</v>
       </c>
       <c r="G66">
-        <v>-6.101051872628754</v>
+        <v>-8.506974290566394</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.88654858427022</v>
       </c>
       <c r="E67">
-        <v>-13.80774047417724</v>
+        <v>-19.74989538366609</v>
       </c>
       <c r="F67">
-        <v>-0.2791972385240671</v>
+        <v>-0.6128023291839009</v>
       </c>
       <c r="G67">
-        <v>-6.565289673600753</v>
+        <v>-8.379402418210578</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.9697073525369</v>
       </c>
       <c r="E68">
-        <v>-13.93877639806318</v>
+        <v>-19.45800806302769</v>
       </c>
       <c r="F68">
-        <v>-0.4454331805504691</v>
+        <v>-0.6888050383907555</v>
       </c>
       <c r="G68">
-        <v>-6.305269495309776</v>
+        <v>-8.416447422795022</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.0011212724061</v>
       </c>
       <c r="E69">
-        <v>-14.40295404079741</v>
+        <v>-19.39046587320329</v>
       </c>
       <c r="F69">
-        <v>-0.2449243656006404</v>
+        <v>-0.6396381195649936</v>
       </c>
       <c r="G69">
-        <v>-6.375909916026744</v>
+        <v>-8.508805022249611</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.97132596720932</v>
       </c>
       <c r="E70">
-        <v>-14.72179483872947</v>
+        <v>-19.20779176020788</v>
       </c>
       <c r="F70">
-        <v>-0.209736975064523</v>
+        <v>-0.933758249602986</v>
       </c>
       <c r="G70">
-        <v>-6.551097364873898</v>
+        <v>-8.467423203008721</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.88537169593849</v>
       </c>
       <c r="E71">
-        <v>-14.42416088457533</v>
+        <v>-19.08375685713779</v>
       </c>
       <c r="F71">
-        <v>-0.7773715959958702</v>
+        <v>-1.013329565581101</v>
       </c>
       <c r="G71">
-        <v>-6.373969936340732</v>
+        <v>-8.310106078982553</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.74549230458009</v>
       </c>
       <c r="E72">
-        <v>-14.62196462923037</v>
+        <v>-19.28211760409577</v>
       </c>
       <c r="F72">
-        <v>-0.4832083908529322</v>
+        <v>-1.057446756719397</v>
       </c>
       <c r="G72">
-        <v>-6.178502085520003</v>
+        <v>-7.615523829933605</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.56321421638156</v>
       </c>
       <c r="E73">
-        <v>-14.71103518448724</v>
+        <v>-19.47158442810269</v>
       </c>
       <c r="F73">
-        <v>-0.6029861754607266</v>
+        <v>-1.53776648319126</v>
       </c>
       <c r="G73">
-        <v>-6.342493269353342</v>
+        <v>-7.729681371764293</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.34882118171569</v>
       </c>
       <c r="E74">
-        <v>-14.54797389241905</v>
+        <v>-19.1899767434617</v>
       </c>
       <c r="F74">
-        <v>-0.6509850962485413</v>
+        <v>-1.340808050929829</v>
       </c>
       <c r="G74">
-        <v>-5.865768090607212</v>
+        <v>-8.496215017563761</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.11584924876511</v>
       </c>
       <c r="E75">
-        <v>-14.52449828316328</v>
+        <v>-19.82227398373069</v>
       </c>
       <c r="F75">
-        <v>-0.9245898791888011</v>
+        <v>-1.1751262866959</v>
       </c>
       <c r="G75">
-        <v>-6.389910213112323</v>
+        <v>-8.558751222800595</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.87741626150519</v>
       </c>
       <c r="E76">
-        <v>-15.22668346279265</v>
+        <v>-19.6629939674589</v>
       </c>
       <c r="F76">
-        <v>-0.8912969649028862</v>
+        <v>-1.309711138628736</v>
       </c>
       <c r="G76">
-        <v>-6.279784915748467</v>
+        <v>-8.306289019975774</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.64232796998157</v>
       </c>
       <c r="E77">
-        <v>-15.36010589248064</v>
+        <v>-20.29620143100343</v>
       </c>
       <c r="F77">
-        <v>-0.6479135099189607</v>
+        <v>-1.417311094047975</v>
       </c>
       <c r="G77">
-        <v>-5.852396797174095</v>
+        <v>-7.818344402397054</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.42101506227728</v>
       </c>
       <c r="E78">
-        <v>-15.0371396547276</v>
+        <v>-20.43107750084788</v>
       </c>
       <c r="F78">
-        <v>-1.035547207691587</v>
+        <v>-1.814891827593417</v>
       </c>
       <c r="G78">
-        <v>-5.776052306492963</v>
+        <v>-8.080652167655668</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.21488679399509</v>
       </c>
       <c r="E79">
-        <v>-15.68760513271536</v>
+        <v>-19.88314573134179</v>
       </c>
       <c r="F79">
-        <v>-1.217251254230464</v>
+        <v>-1.760181474108121</v>
       </c>
       <c r="G79">
-        <v>-5.723378216417618</v>
+        <v>-7.65692882299327</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.03028510395951</v>
       </c>
       <c r="E80">
-        <v>-16.86138106702951</v>
+        <v>-20.64268856275231</v>
       </c>
       <c r="F80">
-        <v>-0.9856264745292771</v>
+        <v>-1.963234205351947</v>
       </c>
       <c r="G80">
-        <v>-5.159529410714489</v>
+        <v>-7.786261905575977</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.86272855832503</v>
       </c>
       <c r="E81">
-        <v>-17.41580213978859</v>
+        <v>-21.51509908033001</v>
       </c>
       <c r="F81">
-        <v>-1.373283366589181</v>
+        <v>-1.993077797772605</v>
       </c>
       <c r="G81">
-        <v>-5.541821277952908</v>
+        <v>-7.546843252175885</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.7158824433123</v>
       </c>
       <c r="E82">
-        <v>-18.29727866232964</v>
+        <v>-21.84317796523771</v>
       </c>
       <c r="F82">
-        <v>-1.22349962954978</v>
+        <v>-1.714931904730198</v>
       </c>
       <c r="G82">
-        <v>-4.99377370610872</v>
+        <v>-7.451582304283357</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.57989281285497</v>
       </c>
       <c r="E83">
-        <v>-18.46616810044571</v>
+        <v>-21.74975554645947</v>
       </c>
       <c r="F83">
-        <v>-1.500682959670134</v>
+        <v>-1.800879164607661</v>
       </c>
       <c r="G83">
-        <v>-5.096910441839175</v>
+        <v>-7.254042051955045</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.4548783092816</v>
       </c>
       <c r="E84">
-        <v>-19.25973788554986</v>
+        <v>-24.29134346936843</v>
       </c>
       <c r="F84">
-        <v>-1.660751706382694</v>
+        <v>-2.104322569764162</v>
       </c>
       <c r="G84">
-        <v>-4.892676266430457</v>
+        <v>-6.73918269914205</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.32709658633995</v>
       </c>
       <c r="E85">
-        <v>-20.3578792469879</v>
+        <v>-24.2970538750921</v>
       </c>
       <c r="F85">
-        <v>-1.575270817353007</v>
+        <v>-2.604421224712668</v>
       </c>
       <c r="G85">
-        <v>-4.757774846250696</v>
+        <v>-6.820794267776164</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.19487451665596</v>
       </c>
       <c r="E86">
-        <v>-20.97269204911327</v>
+        <v>-25.33181018584478</v>
       </c>
       <c r="F86">
-        <v>-1.829946576771896</v>
+        <v>-2.602625324183399</v>
       </c>
       <c r="G86">
-        <v>-4.460428267004436</v>
+        <v>-6.952163335865523</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.04468670518809</v>
       </c>
       <c r="E87">
-        <v>-21.59196992661021</v>
+        <v>-26.72518088173888</v>
       </c>
       <c r="F87">
-        <v>-1.981316637387658</v>
+        <v>-2.686736921896258</v>
       </c>
       <c r="G87">
-        <v>-4.504190368488062</v>
+        <v>-7.780157259601561</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.87730119803068</v>
       </c>
       <c r="E88">
-        <v>-23.31400820903301</v>
+        <v>-26.89930523580781</v>
       </c>
       <c r="F88">
-        <v>-2.157449913142708</v>
+        <v>-2.79657181256825</v>
       </c>
       <c r="G88">
-        <v>-4.595743505376606</v>
+        <v>-6.995432166063797</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.68343191049112</v>
       </c>
       <c r="E89">
-        <v>-24.72417501502156</v>
+        <v>-28.90109452852845</v>
       </c>
       <c r="F89">
-        <v>-2.331162699346779</v>
+        <v>-2.603005544821284</v>
       </c>
       <c r="G89">
-        <v>-4.153517521695222</v>
+        <v>-6.712526186459839</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.4678576707589</v>
       </c>
       <c r="E90">
-        <v>-25.9194385585021</v>
+        <v>-29.69282575318549</v>
       </c>
       <c r="F90">
-        <v>-2.322325675893713</v>
+        <v>-2.884656260344935</v>
       </c>
       <c r="G90">
-        <v>-4.309543532961073</v>
+        <v>-6.675130264048232</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.22750378240277</v>
       </c>
       <c r="E91">
-        <v>-27.79967455190886</v>
+        <v>-30.6467193678202</v>
       </c>
       <c r="F91">
-        <v>-2.559618145364854</v>
+        <v>-3.352449414951664</v>
       </c>
       <c r="G91">
-        <v>-4.234933768142518</v>
+        <v>-6.176274088372074</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.97185489360264</v>
       </c>
       <c r="E92">
-        <v>-29.3757918163825</v>
+        <v>-33.11555509155893</v>
       </c>
       <c r="F92">
-        <v>-2.808888807480476</v>
+        <v>-3.534669534382485</v>
       </c>
       <c r="G92">
-        <v>-4.187443992381673</v>
+        <v>-7.126096087953292</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.70572145011893</v>
       </c>
       <c r="E93">
-        <v>-31.19615232645983</v>
+        <v>-34.34781400344514</v>
       </c>
       <c r="F93">
-        <v>-2.879755638789974</v>
+        <v>-3.509477224928546</v>
       </c>
       <c r="G93">
-        <v>-3.967719774394705</v>
+        <v>-6.827911940685597</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.44300603123679</v>
       </c>
       <c r="E94">
-        <v>-32.92113864546162</v>
+        <v>-35.78783930280326</v>
       </c>
       <c r="F94">
-        <v>-3.079142015909009</v>
+        <v>-3.353498956451011</v>
       </c>
       <c r="G94">
-        <v>-4.624197644286642</v>
+        <v>-6.758486490181541</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.19521242602757</v>
       </c>
       <c r="E95">
-        <v>-35.18296423688772</v>
+        <v>-37.6513561701737</v>
       </c>
       <c r="F95">
-        <v>-3.104112322898997</v>
+        <v>-3.969287402874496</v>
       </c>
       <c r="G95">
-        <v>-4.320418675057579</v>
+        <v>-6.728118855949806</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.98106763803035</v>
       </c>
       <c r="E96">
-        <v>-36.96936798461854</v>
+        <v>-39.88370592428387</v>
       </c>
       <c r="F96">
-        <v>-3.413148036391798</v>
+        <v>-4.127548651914148</v>
       </c>
       <c r="G96">
-        <v>-4.604486656145822</v>
+        <v>-7.837492597796198</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.81116881572605</v>
       </c>
       <c r="E97">
-        <v>-38.83802693422469</v>
+        <v>-41.4876846250897</v>
       </c>
       <c r="F97">
-        <v>-3.682302001276816</v>
+        <v>-4.434914376722904</v>
       </c>
       <c r="G97">
-        <v>-5.302869411473853</v>
+        <v>-7.227799357465242</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.70692807513578</v>
       </c>
       <c r="E98">
-        <v>-40.92975851344868</v>
+        <v>-43.26537106035575</v>
       </c>
       <c r="F98">
-        <v>-3.555107014944354</v>
+        <v>-4.734836392050104</v>
       </c>
       <c r="G98">
-        <v>-5.663344783608475</v>
+        <v>-7.18056780425646</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.66627660235367</v>
       </c>
       <c r="E99">
-        <v>-43.24091277224033</v>
+        <v>-46.17585300440354</v>
       </c>
       <c r="F99">
-        <v>-3.861536684587947</v>
+        <v>-4.641281405945331</v>
       </c>
       <c r="G99">
-        <v>-6.146896307256582</v>
+        <v>-8.246288692622024</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.714836531485</v>
       </c>
       <c r="E100">
-        <v>-46.56517950026499</v>
+        <v>-48.42081682286208</v>
       </c>
       <c r="F100">
-        <v>-3.984542616964452</v>
+        <v>-4.949523543466249</v>
       </c>
       <c r="G100">
-        <v>-5.731485742443294</v>
+        <v>-8.496748015395584</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.81839493624162</v>
       </c>
       <c r="E101">
-        <v>-48.48424262981351</v>
+        <v>-49.87455660575243</v>
       </c>
       <c r="F101">
-        <v>-4.157436147807153</v>
+        <v>-5.157519143002579</v>
       </c>
       <c r="G101">
-        <v>-6.505723027712646</v>
+        <v>-8.719865542560305</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.03047024167201</v>
       </c>
       <c r="E102">
-        <v>-50.70535610779215</v>
+        <v>-52.6777522078475</v>
       </c>
       <c r="F102">
-        <v>-4.236416837827072</v>
+        <v>-5.152191083867773</v>
       </c>
       <c r="G102">
-        <v>-6.954186079190018</v>
+        <v>-9.048645751701946</v>
       </c>
     </row>
   </sheetData>
